--- a/spreadsheets/03_MAD/M0111C/M0111C.xlsx
+++ b/spreadsheets/03_MAD/M0111C/M0111C.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e255fabf6a46c9b0/Desktop/Work stuff/SURF 2026/MAD-FF-Corrections-from-Varied-Salinity/spreadsheets/03_MAD/M0111C/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{B96E9D15-E3D1-4FE3-AD8D-4DA11EC31CAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="14_{B96E9D15-E3D1-4FE3-AD8D-4DA11EC31CAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{542A4EAE-4A76-45D2-84D3-AF45A3AD7D98}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MAD" sheetId="2" r:id="rId1"/>
@@ -1213,23 +1213,23 @@
         <v>0.10669284876080855</v>
       </c>
       <c r="AH2" s="15">
-        <f t="shared" ref="AH2:AH36" si="14">V2/AD2</f>
+        <f>V2/AD2</f>
         <v>2.3838856799498038</v>
       </c>
       <c r="AI2" s="15">
-        <f t="shared" ref="AI2:AI36" si="15">Z2/AD2</f>
+        <f t="shared" ref="AI2:AI36" si="14">Z2/AD2</f>
         <v>2.1540626042890763</v>
       </c>
       <c r="AJ2" s="15">
-        <f t="shared" ref="AJ2:AJ36" si="16">Z2/AE2</f>
+        <f t="shared" ref="AJ2:AJ36" si="15">Z2/AE2</f>
         <v>2.7774165166371838</v>
       </c>
       <c r="AK2" s="15">
-        <f t="shared" ref="AK2:AK36" si="17">AA2/AD2</f>
+        <f t="shared" ref="AK2:AK36" si="16">AA2/AD2</f>
         <v>0.22443659732492943</v>
       </c>
       <c r="AL2" s="15">
-        <f t="shared" ref="AL2:AL36" si="18">AA2/AE2</f>
+        <f t="shared" ref="AL2:AL36" si="17">AA2/AE2</f>
         <v>0.28938523472201438</v>
       </c>
       <c r="AM2" s="14" t="s">
@@ -1307,7 +1307,7 @@
         <v>9.8641000000000005</v>
       </c>
       <c r="W3" s="15">
-        <f t="shared" ref="W3:W36" si="19">Q3-N3</f>
+        <f t="shared" ref="W3:W36" si="18">Q3-N3</f>
         <v>6.8302000000000014</v>
       </c>
       <c r="X3" s="15">
@@ -1351,23 +1351,23 @@
         <v>0.46783659998336136</v>
       </c>
       <c r="AH3" s="15">
+        <f t="shared" ref="AH2:AH36" si="19">V3/AD3</f>
+        <v>1.7696383773702855</v>
+      </c>
+      <c r="AI3" s="15">
         <f t="shared" si="14"/>
-        <v>1.7696383773702855</v>
-      </c>
-      <c r="AI3" s="15">
+        <v>1.2056099278287142</v>
+      </c>
+      <c r="AJ3" s="15">
         <f t="shared" si="15"/>
-        <v>1.2056099278287142</v>
-      </c>
-      <c r="AJ3" s="15">
+        <v>2.6839585293181711</v>
+      </c>
+      <c r="AK3" s="15">
         <f t="shared" si="16"/>
-        <v>2.6839585293181711</v>
-      </c>
-      <c r="AK3" s="15">
+        <v>0.55080903275544069</v>
+      </c>
+      <c r="AL3" s="15">
         <f t="shared" si="17"/>
-        <v>0.55080903275544069</v>
-      </c>
-      <c r="AL3" s="15">
-        <f t="shared" si="18"/>
         <v>1.2262246414575741</v>
       </c>
       <c r="AM3" s="14" t="s">
@@ -1445,7 +1445,7 @@
         <v>9.7614999999999998</v>
       </c>
       <c r="W4" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>6.8068000000000008</v>
       </c>
       <c r="X4" s="15">
@@ -1489,23 +1489,23 @@
         <v>0.45701973543527025</v>
       </c>
       <c r="AH4" s="15">
+        <f t="shared" si="19"/>
+        <v>1.781515128685941</v>
+      </c>
+      <c r="AI4" s="15">
         <f t="shared" si="14"/>
-        <v>1.781515128685941</v>
-      </c>
-      <c r="AI4" s="15">
+        <v>1.2227117350292658</v>
+      </c>
+      <c r="AJ4" s="15">
         <f t="shared" si="15"/>
-        <v>1.2227117350292658</v>
-      </c>
-      <c r="AJ4" s="15">
+        <v>2.6914573313673831</v>
+      </c>
+      <c r="AK4" s="15">
         <f t="shared" si="16"/>
-        <v>2.6914573313673831</v>
-      </c>
-      <c r="AK4" s="15">
+        <v>0.545706439117847</v>
+      </c>
+      <c r="AL4" s="15">
         <f t="shared" si="17"/>
-        <v>0.545706439117847</v>
-      </c>
-      <c r="AL4" s="15">
-        <f t="shared" si="18"/>
         <v>1.201219841325039</v>
       </c>
       <c r="AM4" s="14" t="s">
@@ -1583,7 +1583,7 @@
         <v>10.729800000000001</v>
       </c>
       <c r="W5" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>8.622399999999999</v>
       </c>
       <c r="X5" s="15">
@@ -1627,23 +1627,23 @@
         <v>0.25553977715389053</v>
       </c>
       <c r="AH5" s="15">
+        <f t="shared" si="19"/>
+        <v>2.0307906210284825</v>
+      </c>
+      <c r="AI5" s="15">
         <f t="shared" si="14"/>
-        <v>2.0307906210284825</v>
-      </c>
-      <c r="AI5" s="15">
+        <v>1.6174641839161501</v>
+      </c>
+      <c r="AJ5" s="15">
         <f t="shared" si="15"/>
-        <v>1.6174641839161501</v>
-      </c>
-      <c r="AJ5" s="15">
+        <v>2.7122237230937869</v>
+      </c>
+      <c r="AK5" s="15">
         <f t="shared" si="16"/>
-        <v>2.7122237230937869</v>
-      </c>
-      <c r="AK5" s="15">
+        <v>0.40363909874251214</v>
+      </c>
+      <c r="AL5" s="15">
         <f t="shared" si="17"/>
-        <v>0.40363909874251214</v>
-      </c>
-      <c r="AL5" s="15">
-        <f t="shared" si="18"/>
         <v>0.67683695878015782</v>
       </c>
       <c r="AM5" s="14" t="s">
@@ -1721,7 +1721,7 @@
         <v>10.077500000000001</v>
       </c>
       <c r="W6" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>7.3190999999999988</v>
       </c>
       <c r="X6" s="15">
@@ -1765,23 +1765,23 @@
         <v>0.39595845048814787</v>
       </c>
       <c r="AH6" s="15">
+        <f t="shared" si="19"/>
+        <v>1.8526598430797783</v>
+      </c>
+      <c r="AI6" s="15">
         <f t="shared" si="14"/>
-        <v>1.8526598430797783</v>
-      </c>
-      <c r="AI6" s="15">
+        <v>1.3271597320335202</v>
+      </c>
+      <c r="AJ6" s="15">
         <f t="shared" si="15"/>
-        <v>1.3271597320335202</v>
-      </c>
-      <c r="AJ6" s="15">
+        <v>2.726202343704903</v>
+      </c>
+      <c r="AK6" s="15">
         <f t="shared" si="16"/>
-        <v>2.726202343704903</v>
-      </c>
-      <c r="AK6" s="15">
+        <v>0.51318370219361154</v>
+      </c>
+      <c r="AL6" s="15">
         <f t="shared" si="17"/>
-        <v>0.51318370219361154</v>
-      </c>
-      <c r="AL6" s="15">
-        <f t="shared" si="18"/>
         <v>1.0541629450493657</v>
       </c>
       <c r="AM6" s="14" t="s">
@@ -1859,7 +1859,7 @@
         <v>9.6953000000000014</v>
       </c>
       <c r="W7" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>7.6834000000000007</v>
       </c>
       <c r="X7" s="15">
@@ -1903,23 +1903,23 @@
         <v>0.27394911904708907</v>
       </c>
       <c r="AH7" s="15">
+        <f t="shared" si="19"/>
+        <v>1.9998578451891404</v>
+      </c>
+      <c r="AI7" s="15">
         <f t="shared" si="14"/>
-        <v>1.9998578451891404</v>
-      </c>
-      <c r="AI7" s="15">
+        <v>1.5698098262236952</v>
+      </c>
+      <c r="AJ7" s="15">
         <f t="shared" si="15"/>
-        <v>1.5698098262236952</v>
-      </c>
-      <c r="AJ7" s="15">
+        <v>2.706422932125121</v>
+      </c>
+      <c r="AK7" s="15">
         <f t="shared" si="16"/>
-        <v>2.706422932125121</v>
-      </c>
-      <c r="AK7" s="15">
+        <v>0.41996876852094261</v>
+      </c>
+      <c r="AL7" s="15">
         <f t="shared" si="17"/>
-        <v>0.41996876852094261</v>
-      </c>
-      <c r="AL7" s="15">
-        <f t="shared" si="18"/>
         <v>0.72404509572706699</v>
       </c>
       <c r="AM7" s="14" t="s">
@@ -1997,7 +1997,7 @@
         <v>11.388899999999998</v>
       </c>
       <c r="W8" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>9.0169999999999977</v>
       </c>
       <c r="X8" s="15">
@@ -2041,23 +2041,23 @@
         <v>0.27521386393755642</v>
       </c>
       <c r="AH8" s="15">
+        <f t="shared" si="19"/>
+        <v>2.0136039796009522</v>
+      </c>
+      <c r="AI8" s="15">
         <f t="shared" si="14"/>
-        <v>2.0136039796009522</v>
-      </c>
-      <c r="AI8" s="15">
+        <v>1.5790323776620674</v>
+      </c>
+      <c r="AJ8" s="15">
         <f t="shared" si="15"/>
-        <v>1.5790323776620674</v>
-      </c>
-      <c r="AJ8" s="15">
+        <v>2.7432155628143042</v>
+      </c>
+      <c r="AK8" s="15">
         <f t="shared" si="16"/>
-        <v>2.7432155628143042</v>
-      </c>
-      <c r="AK8" s="15">
+        <v>0.42438633001844184</v>
+      </c>
+      <c r="AL8" s="15">
         <f t="shared" si="17"/>
-        <v>0.42438633001844184</v>
-      </c>
-      <c r="AL8" s="15">
-        <f t="shared" si="18"/>
         <v>0.73727632290601874</v>
       </c>
       <c r="AM8" s="14" t="s">
@@ -2135,7 +2135,7 @@
         <v>11.190300000000001</v>
       </c>
       <c r="W9" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>8.7332999999999998</v>
       </c>
       <c r="X9" s="15">
@@ -2179,23 +2179,23 @@
         <v>0.29454641380750157</v>
       </c>
       <c r="AH9" s="15">
+        <f t="shared" si="19"/>
+        <v>1.9749188767851542</v>
+      </c>
+      <c r="AI9" s="15">
         <f t="shared" si="14"/>
-        <v>1.9749188767851542</v>
-      </c>
-      <c r="AI9" s="15">
+        <v>1.5255682266165731</v>
+      </c>
+      <c r="AJ9" s="15">
         <f t="shared" si="15"/>
-        <v>1.5255682266165731</v>
-      </c>
-      <c r="AJ9" s="15">
+        <v>2.7184958349185617</v>
+      </c>
+      <c r="AK9" s="15">
         <f t="shared" si="16"/>
-        <v>2.7184958349185617</v>
-      </c>
-      <c r="AK9" s="15">
+        <v>0.43881899430525534</v>
+      </c>
+      <c r="AL9" s="15">
         <f t="shared" si="17"/>
-        <v>0.43881899430525534</v>
-      </c>
-      <c r="AL9" s="15">
-        <f t="shared" si="18"/>
         <v>0.78195624914637907</v>
       </c>
       <c r="AM9" s="14" t="s">
@@ -2273,7 +2273,7 @@
         <v>9.6170999999999989</v>
       </c>
       <c r="W10" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>6.5950000000000006</v>
       </c>
       <c r="X10" s="15">
@@ -2317,23 +2317,23 @@
         <v>0.48288688413487024</v>
       </c>
       <c r="AH10" s="15">
+        <f t="shared" si="19"/>
+        <v>1.7490148867070439</v>
+      </c>
+      <c r="AI10" s="15">
         <f t="shared" si="14"/>
-        <v>1.7490148867070439</v>
-      </c>
-      <c r="AI10" s="15">
+        <v>1.1794661517472622</v>
+      </c>
+      <c r="AJ10" s="15">
         <f t="shared" si="15"/>
-        <v>1.1794661517472622</v>
-      </c>
-      <c r="AJ10" s="15">
+        <v>2.6576520571073994</v>
+      </c>
+      <c r="AK10" s="15">
         <f t="shared" si="16"/>
-        <v>2.6576520571073994</v>
-      </c>
-      <c r="AK10" s="15">
+        <v>0.55619993648416166</v>
+      </c>
+      <c r="AL10" s="15">
         <f t="shared" si="17"/>
-        <v>0.55619993648416166</v>
-      </c>
-      <c r="AL10" s="15">
-        <f t="shared" si="18"/>
         <v>1.2532669150109572</v>
       </c>
       <c r="AM10" s="14" t="s">
@@ -2411,7 +2411,7 @@
         <v>9.9123000000000001</v>
       </c>
       <c r="W11" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>6.6912000000000003</v>
       </c>
       <c r="X11" s="15">
@@ -2455,23 +2455,23 @@
         <v>0.507718028056658</v>
       </c>
       <c r="AH11" s="15">
+        <f t="shared" si="19"/>
+        <v>1.7107820342843749</v>
+      </c>
+      <c r="AI11" s="15">
         <f t="shared" si="14"/>
-        <v>1.7107820342843749</v>
-      </c>
-      <c r="AI11" s="15">
+        <v>1.1346830126382796</v>
+      </c>
+      <c r="AJ11" s="15">
         <f t="shared" si="15"/>
-        <v>1.1346830126382796</v>
-      </c>
-      <c r="AJ11" s="15">
+        <v>2.5941345544986096</v>
+      </c>
+      <c r="AK11" s="15">
         <f t="shared" si="16"/>
-        <v>2.5941345544986096</v>
-      </c>
-      <c r="AK11" s="15">
+        <v>0.56259670082626489</v>
+      </c>
+      <c r="AL11" s="15">
         <f t="shared" si="17"/>
-        <v>0.56259670082626489</v>
-      </c>
-      <c r="AL11" s="15">
-        <f t="shared" si="18"/>
         <v>1.2862196098863976</v>
       </c>
       <c r="AM11" s="14" t="s">
@@ -2549,7 +2549,7 @@
         <v>7.9960999999999984</v>
       </c>
       <c r="W12" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>5.9893000000000001</v>
       </c>
       <c r="X12" s="15">
@@ -2593,23 +2593,23 @@
         <v>0.35148827734575877</v>
       </c>
       <c r="AH12" s="15">
+        <f t="shared" si="19"/>
+        <v>1.8870862073916395</v>
+      </c>
+      <c r="AI12" s="15">
         <f t="shared" si="14"/>
-        <v>1.8870862073916395</v>
-      </c>
-      <c r="AI12" s="15">
+        <v>1.396302312808634</v>
+      </c>
+      <c r="AJ12" s="15">
         <f t="shared" si="15"/>
-        <v>1.396302312808634</v>
-      </c>
-      <c r="AJ12" s="15">
+        <v>2.6814898383421397</v>
+      </c>
+      <c r="AK12" s="15">
         <f t="shared" si="16"/>
-        <v>2.6814898383421397</v>
-      </c>
-      <c r="AK12" s="15">
+        <v>0.47928114705371644</v>
+      </c>
+      <c r="AL12" s="15">
         <f t="shared" si="17"/>
-        <v>0.47928114705371644</v>
-      </c>
-      <c r="AL12" s="15">
-        <f t="shared" si="18"/>
         <v>0.92042211328030854</v>
       </c>
       <c r="AM12" s="14" t="s">
@@ -2687,7 +2687,7 @@
         <v>9.7214000000000009</v>
       </c>
       <c r="W13" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>7.5298999999999996</v>
       </c>
       <c r="X13" s="15">
@@ -2731,23 +2731,23 @@
         <v>0.30481312653423676</v>
       </c>
       <c r="AH13" s="15">
+        <f t="shared" si="19"/>
+        <v>1.937814058329542</v>
+      </c>
+      <c r="AI13" s="15">
         <f t="shared" si="14"/>
-        <v>1.937814058329542</v>
-      </c>
-      <c r="AI13" s="15">
+        <v>1.48512765462181</v>
+      </c>
+      <c r="AJ13" s="15">
         <f t="shared" si="15"/>
-        <v>1.48512765462181</v>
-      </c>
-      <c r="AJ13" s="15">
+        <v>2.6618843454843142</v>
+      </c>
+      <c r="AK13" s="15">
         <f t="shared" si="16"/>
-        <v>2.6618843454843142</v>
-      </c>
-      <c r="AK13" s="15">
+        <v>0.44207656612083207</v>
+      </c>
+      <c r="AL13" s="15">
         <f t="shared" si="17"/>
-        <v>0.44207656612083207</v>
-      </c>
-      <c r="AL13" s="15">
-        <f t="shared" si="18"/>
         <v>0.79236063458946704</v>
       </c>
       <c r="AM13" s="14" t="s">
@@ -2825,7 +2825,7 @@
         <v>7.8619999999999983</v>
       </c>
       <c r="W14" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>6.2760999999999996</v>
       </c>
       <c r="X14" s="15">
@@ -2869,23 +2869,23 @@
         <v>0.26427570393255689</v>
       </c>
       <c r="AH14" s="15">
+        <f t="shared" si="19"/>
+        <v>2.0067500147818929</v>
+      </c>
+      <c r="AI14" s="15">
         <f t="shared" si="14"/>
-        <v>2.0067500147818929</v>
-      </c>
-      <c r="AI14" s="15">
+        <v>1.5872724663930926</v>
+      </c>
+      <c r="AJ14" s="15">
         <f t="shared" si="15"/>
-        <v>1.5872724663930926</v>
-      </c>
-      <c r="AJ14" s="15">
+        <v>2.6886793058794218</v>
+      </c>
+      <c r="AK14" s="15">
         <f t="shared" si="16"/>
-        <v>2.6886793058794218</v>
-      </c>
-      <c r="AK14" s="15">
+        <v>0.40964604334843779</v>
+      </c>
+      <c r="AL14" s="15">
         <f t="shared" si="17"/>
-        <v>0.40964604334843779</v>
-      </c>
-      <c r="AL14" s="15">
-        <f t="shared" si="18"/>
         <v>0.69389903926775653</v>
       </c>
       <c r="AM14" s="14" t="s">
@@ -2963,7 +2963,7 @@
         <v>8.3443999999999985</v>
       </c>
       <c r="W15" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>6.5479000000000003</v>
       </c>
       <c r="X15" s="15">
@@ -3007,23 +3007,23 @@
         <v>0.2871713913673703</v>
       </c>
       <c r="AH15" s="15">
+        <f t="shared" si="19"/>
+        <v>1.9684612360212932</v>
+      </c>
+      <c r="AI15" s="15">
         <f t="shared" si="14"/>
-        <v>1.9684612360212932</v>
-      </c>
-      <c r="AI15" s="15">
+        <v>1.5292922521609065</v>
+      </c>
+      <c r="AJ15" s="15">
         <f t="shared" si="15"/>
-        <v>1.5292922521609065</v>
-      </c>
-      <c r="AJ15" s="15">
+        <v>2.6776884655497262</v>
+      </c>
+      <c r="AK15" s="15">
         <f t="shared" si="16"/>
-        <v>2.6776884655497262</v>
-      </c>
-      <c r="AK15" s="15">
+        <v>0.42887596080115897</v>
+      </c>
+      <c r="AL15" s="15">
         <f t="shared" si="17"/>
-        <v>0.42887596080115897</v>
-      </c>
-      <c r="AL15" s="15">
-        <f t="shared" si="18"/>
         <v>0.75093312724636097</v>
       </c>
       <c r="AM15" s="14" t="s">
@@ -3101,7 +3101,7 @@
         <v>7.2317</v>
       </c>
       <c r="W16" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>5.4246999999999996</v>
       </c>
       <c r="X16" s="15">
@@ -3145,23 +3145,23 @@
         <v>0.34940894875570694</v>
       </c>
       <c r="AH16" s="15">
+        <f t="shared" si="19"/>
+        <v>1.9091103835424101</v>
+      </c>
+      <c r="AI16" s="15">
         <f t="shared" si="14"/>
-        <v>1.9091103835424101</v>
-      </c>
-      <c r="AI16" s="15">
+        <v>1.414775250529356</v>
+      </c>
+      <c r="AJ16" s="15">
         <f t="shared" si="15"/>
-        <v>1.414775250529356</v>
-      </c>
-      <c r="AJ16" s="15">
+        <v>2.7351820874646875</v>
+      </c>
+      <c r="AK16" s="15">
         <f t="shared" si="16"/>
-        <v>2.7351820874646875</v>
-      </c>
-      <c r="AK16" s="15">
+        <v>0.48274915333306073</v>
+      </c>
+      <c r="AL16" s="15">
         <f t="shared" si="17"/>
-        <v>0.48274915333306073</v>
-      </c>
-      <c r="AL16" s="15">
-        <f t="shared" si="18"/>
         <v>0.93329794710593406</v>
       </c>
       <c r="AM16" s="14" t="s">
@@ -3239,7 +3239,7 @@
         <v>8.3973999999999993</v>
       </c>
       <c r="W17" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>6.4028000000000009</v>
       </c>
       <c r="X17" s="15">
@@ -3283,23 +3283,23 @@
         <v>0.32650770819122454</v>
       </c>
       <c r="AH17" s="15">
+        <f t="shared" si="19"/>
+        <v>1.9091105653562004</v>
+      </c>
+      <c r="AI17" s="15">
         <f t="shared" si="14"/>
-        <v>1.9091105653562004</v>
-      </c>
-      <c r="AI17" s="15">
+        <v>1.4392005063878528</v>
+      </c>
+      <c r="AJ17" s="15">
         <f t="shared" si="15"/>
-        <v>1.4392005063878528</v>
-      </c>
-      <c r="AJ17" s="15">
+        <v>2.6597510790346099</v>
+      </c>
+      <c r="AK17" s="15">
         <f t="shared" si="16"/>
-        <v>2.6597510790346099</v>
-      </c>
-      <c r="AK17" s="15">
+        <v>0.45889654196127694</v>
+      </c>
+      <c r="AL17" s="15">
         <f t="shared" si="17"/>
-        <v>0.45889654196127694</v>
-      </c>
-      <c r="AL17" s="15">
-        <f t="shared" si="18"/>
         <v>0.84807541911594431</v>
       </c>
       <c r="AM17" s="14" t="s">
@@ -3377,7 +3377,7 @@
         <v>10.643600000000001</v>
       </c>
       <c r="W18" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>8.0041999999999991</v>
       </c>
       <c r="X18" s="15">
@@ -3421,23 +3421,23 @@
         <v>0.34584810619531214</v>
       </c>
       <c r="AH18" s="15">
+        <f t="shared" si="19"/>
+        <v>1.8940736827383786</v>
+      </c>
+      <c r="AI18" s="15">
         <f t="shared" si="14"/>
-        <v>1.8940736827383786</v>
-      </c>
-      <c r="AI18" s="15">
+        <v>1.4073458022635927</v>
+      </c>
+      <c r="AJ18" s="15">
         <f t="shared" si="15"/>
-        <v>1.4073458022635927</v>
-      </c>
-      <c r="AJ18" s="15">
+        <v>2.6822945936435976</v>
+      </c>
+      <c r="AK18" s="15">
         <f t="shared" si="16"/>
-        <v>2.6822945936435976</v>
-      </c>
-      <c r="AK18" s="15">
+        <v>0.47532019577615797</v>
+      </c>
+      <c r="AL18" s="15">
         <f t="shared" si="17"/>
-        <v>0.47532019577615797</v>
-      </c>
-      <c r="AL18" s="15">
-        <f t="shared" si="18"/>
         <v>0.9059243217476195</v>
       </c>
       <c r="AM18" s="14" t="s">
@@ -3515,7 +3515,7 @@
         <v>10.079599999999999</v>
       </c>
       <c r="W19" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>7.3852000000000011</v>
       </c>
       <c r="X19" s="15">
@@ -3559,23 +3559,23 @@
         <v>0.38314012798450114</v>
       </c>
       <c r="AH19" s="15">
+        <f t="shared" si="19"/>
+        <v>1.8127273103608466</v>
+      </c>
+      <c r="AI19" s="15">
         <f t="shared" si="14"/>
-        <v>1.8127273103608466</v>
-      </c>
-      <c r="AI19" s="15">
+        <v>1.3105883299057599</v>
+      </c>
+      <c r="AJ19" s="15">
         <f t="shared" si="15"/>
-        <v>1.3105883299057599</v>
-      </c>
-      <c r="AJ19" s="15">
+        <v>2.5716472385575386</v>
+      </c>
+      <c r="AK19" s="15">
         <f t="shared" si="16"/>
-        <v>2.5716472385575386</v>
-      </c>
-      <c r="AK19" s="15">
+        <v>0.49037009810067039</v>
+      </c>
+      <c r="AL19" s="15">
         <f t="shared" si="17"/>
-        <v>0.49037009810067039</v>
-      </c>
-      <c r="AL19" s="15">
-        <f t="shared" si="18"/>
         <v>0.96220825401555099</v>
       </c>
       <c r="AM19" s="14" t="s">
@@ -3653,7 +3653,7 @@
         <v>8.5733999999999995</v>
       </c>
       <c r="W20" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>6.0196000000000005</v>
       </c>
       <c r="X20" s="15">
@@ -3697,23 +3697,23 @@
         <v>0.44650514176774275</v>
       </c>
       <c r="AH20" s="15">
+        <f t="shared" si="19"/>
+        <v>1.7498719955994253</v>
+      </c>
+      <c r="AI20" s="15">
         <f t="shared" si="14"/>
-        <v>1.7498719955994253</v>
-      </c>
-      <c r="AI20" s="15">
+        <v>1.2097240065534398</v>
+      </c>
+      <c r="AJ20" s="15">
         <f t="shared" si="15"/>
-        <v>1.2097240065534398</v>
-      </c>
-      <c r="AJ20" s="15">
+        <v>2.5601988927735477</v>
+      </c>
+      <c r="AK20" s="15">
         <f t="shared" si="16"/>
-        <v>2.5601988927735477</v>
-      </c>
-      <c r="AK20" s="15">
+        <v>0.52748827055272007</v>
+      </c>
+      <c r="AL20" s="15">
         <f t="shared" si="17"/>
-        <v>0.52748827055272007</v>
-      </c>
-      <c r="AL20" s="15">
-        <f t="shared" si="18"/>
         <v>1.1163495796596397</v>
       </c>
       <c r="AM20" s="14" t="s">
@@ -3791,7 +3791,7 @@
         <v>10.870999999999999</v>
       </c>
       <c r="W21" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>8.0640000000000001</v>
       </c>
       <c r="X21" s="15">
@@ -3835,23 +3835,23 @@
         <v>0.36532758769911927</v>
       </c>
       <c r="AH21" s="15">
+        <f t="shared" si="19"/>
+        <v>1.8255282171177278</v>
+      </c>
+      <c r="AI21" s="15">
         <f t="shared" si="14"/>
-        <v>1.8255282171177278</v>
-      </c>
-      <c r="AI21" s="15">
+        <v>1.3370624263105597</v>
+      </c>
+      <c r="AJ21" s="15">
         <f t="shared" si="15"/>
-        <v>1.3370624263105597</v>
-      </c>
-      <c r="AJ21" s="15">
+        <v>2.5566096451721116</v>
+      </c>
+      <c r="AK21" s="15">
         <f t="shared" si="16"/>
-        <v>2.5566096451721116</v>
-      </c>
-      <c r="AK21" s="15">
+        <v>0.47701737383512521</v>
+      </c>
+      <c r="AL21" s="15">
         <f t="shared" si="17"/>
-        <v>0.47701737383512521</v>
-      </c>
-      <c r="AL21" s="15">
-        <f t="shared" si="18"/>
         <v>0.91210940855373901</v>
       </c>
       <c r="AM21" s="14" t="s">
@@ -3929,7 +3929,7 @@
         <v>10.470799999999999</v>
       </c>
       <c r="W22" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>7.5982000000000003</v>
       </c>
       <c r="X22" s="15">
@@ -3973,23 +3973,23 @@
         <v>0.39722212773112664</v>
       </c>
       <c r="AH22" s="15">
+        <f t="shared" si="19"/>
+        <v>1.7794248003875808</v>
+      </c>
+      <c r="AI22" s="15">
         <f t="shared" si="14"/>
-        <v>1.7794248003875808</v>
-      </c>
-      <c r="AI22" s="15">
+        <v>1.2735446748736312</v>
+      </c>
+      <c r="AJ22" s="15">
         <f t="shared" si="15"/>
-        <v>1.2735446748736312</v>
-      </c>
-      <c r="AJ22" s="15">
+        <v>2.5170039044810077</v>
+      </c>
+      <c r="AK22" s="15">
         <f t="shared" si="16"/>
-        <v>2.5170039044810077</v>
-      </c>
-      <c r="AK22" s="15">
+        <v>0.49402356007221643</v>
+      </c>
+      <c r="AL22" s="15">
         <f t="shared" si="17"/>
-        <v>0.49402356007221643</v>
-      </c>
-      <c r="AL22" s="15">
-        <f t="shared" si="18"/>
         <v>0.97637660785693292</v>
       </c>
       <c r="AM22" s="14" t="s">
@@ -4067,7 +4067,7 @@
         <v>9.3802000000000003</v>
       </c>
       <c r="W23" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>7.0103999999999989</v>
       </c>
       <c r="X23" s="15">
@@ -4111,23 +4111,23 @@
         <v>0.35464935911547502</v>
       </c>
       <c r="AH23" s="15">
+        <f t="shared" si="19"/>
+        <v>1.8560747039728032</v>
+      </c>
+      <c r="AI23" s="15">
         <f t="shared" si="14"/>
-        <v>1.8560747039728032</v>
-      </c>
-      <c r="AI23" s="15">
+        <v>1.370151391194498</v>
+      </c>
+      <c r="AJ23" s="15">
         <f t="shared" si="15"/>
-        <v>1.370151391194498</v>
-      </c>
-      <c r="AJ23" s="15">
+        <v>2.6075001164380436</v>
+      </c>
+      <c r="AK23" s="15">
         <f t="shared" si="16"/>
-        <v>2.6075001164380436</v>
-      </c>
-      <c r="AK23" s="15">
+        <v>0.47453448513506369</v>
+      </c>
+      <c r="AL23" s="15">
         <f t="shared" si="17"/>
-        <v>0.47453448513506369</v>
-      </c>
-      <c r="AL23" s="15">
-        <f t="shared" si="18"/>
         <v>0.90307445819167842</v>
       </c>
       <c r="AM23" s="14" t="s">
@@ -4205,7 +4205,7 @@
         <v>8.444700000000001</v>
       </c>
       <c r="W24" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>6.1105999999999998</v>
       </c>
       <c r="X24" s="15">
@@ -4249,23 +4249,23 @@
         <v>0.40139049881982686</v>
       </c>
       <c r="AH24" s="15">
+        <f t="shared" si="19"/>
+        <v>1.8087566974371732</v>
+      </c>
+      <c r="AI24" s="15">
         <f t="shared" si="14"/>
-        <v>1.8087566974371732</v>
-      </c>
-      <c r="AI24" s="15">
+        <v>1.2906871417784034</v>
+      </c>
+      <c r="AJ24" s="15">
         <f t="shared" si="15"/>
-        <v>1.2906871417784034</v>
-      </c>
-      <c r="AJ24" s="15">
+        <v>2.6123425620334384</v>
+      </c>
+      <c r="AK24" s="15">
         <f t="shared" si="16"/>
-        <v>2.6123425620334384</v>
-      </c>
-      <c r="AK24" s="15">
+        <v>0.50592730044801748</v>
+      </c>
+      <c r="AL24" s="15">
         <f t="shared" si="17"/>
-        <v>0.50592730044801748</v>
-      </c>
-      <c r="AL24" s="15">
-        <f t="shared" si="18"/>
         <v>1.0239936367801428</v>
       </c>
       <c r="AM24" s="14" t="s">
@@ -4343,7 +4343,7 @@
         <v>9.9422999999999995</v>
       </c>
       <c r="W25" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>7.5457999999999998</v>
       </c>
       <c r="X25" s="15">
@@ -4387,23 +4387,23 @@
         <v>0.33294805461570681</v>
       </c>
       <c r="AH25" s="15">
+        <f t="shared" si="19"/>
+        <v>1.8957900088876478</v>
+      </c>
+      <c r="AI25" s="15">
         <f t="shared" si="14"/>
-        <v>1.8957900088876478</v>
-      </c>
-      <c r="AI25" s="15">
+        <v>1.4222534796633244</v>
+      </c>
+      <c r="AJ25" s="15">
         <f t="shared" si="15"/>
-        <v>1.4222534796633244</v>
-      </c>
-      <c r="AJ25" s="15">
+        <v>2.645747884274682</v>
+      </c>
+      <c r="AK25" s="15">
         <f t="shared" si="16"/>
-        <v>2.645747884274682</v>
-      </c>
-      <c r="AK25" s="15">
+        <v>0.46243801682062846</v>
+      </c>
+      <c r="AL25" s="15">
         <f t="shared" si="17"/>
-        <v>0.46243801682062846</v>
-      </c>
-      <c r="AL25" s="15">
-        <f t="shared" si="18"/>
         <v>0.86025059675085691</v>
       </c>
       <c r="AM25" s="14" t="s">
@@ -4481,7 +4481,7 @@
         <v>11.097299999999999</v>
       </c>
       <c r="W26" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>8.7766999999999999</v>
       </c>
       <c r="X26" s="15">
@@ -4525,23 +4525,23 @@
         <v>0.27664741622984251</v>
       </c>
       <c r="AH26" s="15">
+        <f t="shared" si="19"/>
+        <v>2.0772777979011861</v>
+      </c>
+      <c r="AI26" s="15">
         <f t="shared" si="14"/>
-        <v>2.0772777979011861</v>
-      </c>
-      <c r="AI26" s="15">
+        <v>1.6271350816936925</v>
+      </c>
+      <c r="AJ26" s="15">
         <f t="shared" si="15"/>
-        <v>1.6271350816936925</v>
-      </c>
-      <c r="AJ26" s="15">
+        <v>2.9034855367572474</v>
+      </c>
+      <c r="AK26" s="15">
         <f t="shared" si="16"/>
-        <v>2.9034855367572474</v>
-      </c>
-      <c r="AK26" s="15">
+        <v>0.43959249629638059</v>
+      </c>
+      <c r="AL26" s="15">
         <f t="shared" si="17"/>
-        <v>0.43959249629638059</v>
-      </c>
-      <c r="AL26" s="15">
-        <f t="shared" si="18"/>
         <v>0.78441579277793927</v>
       </c>
       <c r="AM26" s="14" t="s">
@@ -4619,7 +4619,7 @@
         <v>11.1318</v>
       </c>
       <c r="W27" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>8.753400000000001</v>
       </c>
       <c r="X27" s="15">
@@ -4663,23 +4663,23 @@
         <v>0.28436879131426934</v>
       </c>
       <c r="AH27" s="15">
+        <f t="shared" si="19"/>
+        <v>2.0308207377611991</v>
+      </c>
+      <c r="AI27" s="15">
         <f t="shared" si="14"/>
-        <v>2.0308207377611991</v>
-      </c>
-      <c r="AI27" s="15">
+        <v>1.5811819404947547</v>
+      </c>
+      <c r="AJ27" s="15">
         <f t="shared" si="15"/>
-        <v>1.5811819404947547</v>
-      </c>
-      <c r="AJ27" s="15">
+        <v>2.8190105796852341</v>
+      </c>
+      <c r="AK27" s="15">
         <f t="shared" si="16"/>
-        <v>2.8190105796852341</v>
-      </c>
-      <c r="AK27" s="15">
+        <v>0.43910038795551204</v>
+      </c>
+      <c r="AL27" s="15">
         <f t="shared" si="17"/>
-        <v>0.43910038795551204</v>
-      </c>
-      <c r="AL27" s="15">
-        <f t="shared" si="18"/>
         <v>0.78285022582737085</v>
       </c>
       <c r="AM27" s="14" t="s">
@@ -4757,7 +4757,7 @@
         <v>10.465700000000002</v>
       </c>
       <c r="W28" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>8.6143000000000001</v>
       </c>
       <c r="X28" s="15">
@@ -4801,23 +4801,23 @@
         <v>0.22446652373505577</v>
       </c>
       <c r="AH28" s="15">
+        <f t="shared" si="19"/>
+        <v>2.1536299815045092</v>
+      </c>
+      <c r="AI28" s="15">
         <f t="shared" si="14"/>
-        <v>2.1536299815045092</v>
-      </c>
-      <c r="AI28" s="15">
+        <v>1.7588312459006035</v>
+      </c>
+      <c r="AJ28" s="15">
         <f t="shared" si="15"/>
-        <v>1.7588312459006035</v>
-      </c>
-      <c r="AJ28" s="15">
+        <v>2.8624278076282219</v>
+      </c>
+      <c r="AK28" s="15">
         <f t="shared" si="16"/>
-        <v>2.8624278076282219</v>
-      </c>
-      <c r="AK28" s="15">
+        <v>0.38554564023818899</v>
+      </c>
+      <c r="AL28" s="15">
         <f t="shared" si="17"/>
-        <v>0.38554564023818899</v>
-      </c>
-      <c r="AL28" s="15">
-        <f t="shared" si="18"/>
         <v>0.62746017521568742</v>
       </c>
       <c r="AM28" s="14" t="s">
@@ -4898,7 +4898,7 @@
         <v>10.171900000000001</v>
       </c>
       <c r="W29" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>7.3548000000000009</v>
       </c>
       <c r="X29" s="15">
@@ -4942,23 +4942,23 @@
         <v>0.40251280811872509</v>
       </c>
       <c r="AH29" s="15">
+        <f t="shared" si="19"/>
+        <v>1.7688494001232233</v>
+      </c>
+      <c r="AI29" s="15">
         <f t="shared" si="14"/>
-        <v>1.7688494001232233</v>
-      </c>
-      <c r="AI29" s="15">
+        <v>1.2612001757730025</v>
+      </c>
+      <c r="AJ29" s="15">
         <f t="shared" si="15"/>
-        <v>1.2612001757730025</v>
-      </c>
-      <c r="AJ29" s="15">
+        <v>2.501146586574527</v>
+      </c>
+      <c r="AK29" s="15">
         <f t="shared" si="16"/>
-        <v>2.501146586574527</v>
-      </c>
-      <c r="AK29" s="15">
+        <v>0.49575119565451259</v>
+      </c>
+      <c r="AL29" s="15">
         <f t="shared" si="17"/>
-        <v>0.49575119565451259</v>
-      </c>
-      <c r="AL29" s="15">
-        <f t="shared" si="18"/>
         <v>0.98314798445183282</v>
       </c>
       <c r="AM29" s="14" t="s">
@@ -5036,7 +5036,7 @@
         <v>10.390200000000002</v>
       </c>
       <c r="W30" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>8.299100000000001</v>
       </c>
       <c r="X30" s="15">
@@ -5080,23 +5080,23 @@
         <v>0.26351395883002382</v>
       </c>
       <c r="AH30" s="15">
+        <f t="shared" si="19"/>
+        <v>1.9875776526310784</v>
+      </c>
+      <c r="AI30" s="15">
         <f t="shared" si="14"/>
-        <v>1.9875776526310784</v>
-      </c>
-      <c r="AI30" s="15">
+        <v>1.5730555556913006</v>
+      </c>
+      <c r="AJ30" s="15">
         <f t="shared" si="15"/>
-        <v>1.5730555556913006</v>
-      </c>
-      <c r="AJ30" s="15">
+        <v>2.6429323867853629</v>
+      </c>
+      <c r="AK30" s="15">
         <f t="shared" si="16"/>
-        <v>2.6429323867853629</v>
-      </c>
-      <c r="AK30" s="15">
+        <v>0.40480673529275157</v>
+      </c>
+      <c r="AL30" s="15">
         <f t="shared" si="17"/>
-        <v>0.40480673529275157</v>
-      </c>
-      <c r="AL30" s="15">
-        <f t="shared" si="18"/>
         <v>0.68012653922060029</v>
       </c>
       <c r="AM30" s="14" t="s">
@@ -5174,7 +5174,7 @@
         <v>10.595599999999999</v>
       </c>
       <c r="W31" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>9.0043999999999986</v>
       </c>
       <c r="X31" s="15">
@@ -5218,23 +5218,23 @@
         <v>0.1843041695227714</v>
       </c>
       <c r="AH31" s="15">
+        <f t="shared" si="19"/>
+        <v>2.1362478639462719</v>
+      </c>
+      <c r="AI31" s="15">
         <f t="shared" si="14"/>
-        <v>2.1362478639462719</v>
-      </c>
-      <c r="AI31" s="15">
+        <v>1.8038000025002838</v>
+      </c>
+      <c r="AJ31" s="15">
         <f t="shared" si="15"/>
-        <v>1.8038000025002838</v>
-      </c>
-      <c r="AJ31" s="15">
+        <v>2.6709355659320653</v>
+      </c>
+      <c r="AK31" s="15">
         <f t="shared" si="16"/>
-        <v>2.6709355659320653</v>
-      </c>
-      <c r="AK31" s="15">
+        <v>0.32465611469334743</v>
+      </c>
+      <c r="AL31" s="15">
         <f t="shared" si="17"/>
-        <v>0.32465611469334743</v>
-      </c>
-      <c r="AL31" s="15">
-        <f t="shared" si="18"/>
         <v>0.48072711067181906</v>
       </c>
       <c r="AM31" s="14" t="s">
@@ -5312,7 +5312,7 @@
         <v>11.1465</v>
       </c>
       <c r="W32" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>8.8445999999999998</v>
       </c>
       <c r="X32" s="15">
@@ -5356,23 +5356,23 @@
         <v>0.27227009136288516</v>
       </c>
       <c r="AH32" s="15">
+        <f t="shared" si="19"/>
+        <v>1.9851034231358982</v>
+      </c>
+      <c r="AI32" s="15">
         <f t="shared" si="14"/>
-        <v>1.9851034231358982</v>
-      </c>
-      <c r="AI32" s="15">
+        <v>1.5602845941378765</v>
+      </c>
+      <c r="AJ32" s="15">
         <f t="shared" si="15"/>
-        <v>1.5602845941378765</v>
-      </c>
-      <c r="AJ32" s="15">
+        <v>2.6665247536490266</v>
+      </c>
+      <c r="AK32" s="15">
         <f t="shared" si="16"/>
-        <v>2.6665247536490266</v>
-      </c>
-      <c r="AK32" s="15">
+        <v>0.41486213769338065</v>
+      </c>
+      <c r="AL32" s="15">
         <f t="shared" si="17"/>
-        <v>0.41486213769338065</v>
-      </c>
-      <c r="AL32" s="15">
-        <f t="shared" si="18"/>
         <v>0.70899896318106959</v>
       </c>
       <c r="AM32" s="14" t="s">
@@ -5450,7 +5450,7 @@
         <v>11.141400000000001</v>
       </c>
       <c r="W33" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>9.4265000000000008</v>
       </c>
       <c r="X33" s="15">
@@ -5494,23 +5494,23 @@
         <v>0.18977373115030283</v>
       </c>
       <c r="AH33" s="15">
+        <f t="shared" si="19"/>
+        <v>2.1319770197874308</v>
+      </c>
+      <c r="AI33" s="15">
         <f t="shared" si="14"/>
-        <v>2.1319770197874308</v>
-      </c>
-      <c r="AI33" s="15">
+        <v>1.7919180462373989</v>
+      </c>
+      <c r="AJ33" s="15">
         <f t="shared" si="15"/>
-        <v>1.7919180462373989</v>
-      </c>
-      <c r="AJ33" s="15">
+        <v>2.6828688562102592</v>
+      </c>
+      <c r="AK33" s="15">
         <f t="shared" si="16"/>
-        <v>2.6828688562102592</v>
-      </c>
-      <c r="AK33" s="15">
+        <v>0.33208884135745315</v>
+      </c>
+      <c r="AL33" s="15">
         <f t="shared" si="17"/>
-        <v>0.33208884135745315</v>
-      </c>
-      <c r="AL33" s="15">
-        <f t="shared" si="18"/>
         <v>0.49720511038082632</v>
       </c>
       <c r="AM33" s="14" t="s">
@@ -5588,7 +5588,7 @@
         <v>10.277299999999999</v>
       </c>
       <c r="W34" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>8.7092000000000009</v>
       </c>
       <c r="X34" s="15">
@@ -5632,23 +5632,23 @@
         <v>0.18780777686601235</v>
       </c>
       <c r="AH34" s="15">
+        <f t="shared" si="19"/>
+        <v>2.1240743335240921</v>
+      </c>
+      <c r="AI34" s="15">
         <f t="shared" si="14"/>
-        <v>2.1240743335240921</v>
-      </c>
-      <c r="AI34" s="15">
+        <v>1.7882307010385006</v>
+      </c>
+      <c r="AJ34" s="15">
         <f t="shared" si="15"/>
-        <v>1.7882307010385006</v>
-      </c>
-      <c r="AJ34" s="15">
+        <v>2.6609478954288464</v>
+      </c>
+      <c r="AK34" s="15">
         <f t="shared" si="16"/>
-        <v>2.6609478954288464</v>
-      </c>
-      <c r="AK34" s="15">
+        <v>0.32797229734921052</v>
+      </c>
+      <c r="AL34" s="15">
         <f t="shared" si="17"/>
-        <v>0.32797229734921052</v>
-      </c>
-      <c r="AL34" s="15">
-        <f t="shared" si="18"/>
         <v>0.48803389511404882</v>
       </c>
       <c r="AM34" s="14" t="s">
@@ -5726,7 +5726,7 @@
         <v>7.8800999999999988</v>
       </c>
       <c r="W35" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>7.0652000000000008</v>
       </c>
       <c r="X35" s="15">
@@ -5770,23 +5770,23 @@
         <v>0.12002539548249949</v>
       </c>
       <c r="AH35" s="15">
+        <f t="shared" si="19"/>
+        <v>2.263915880756588</v>
+      </c>
+      <c r="AI35" s="15">
         <f t="shared" si="14"/>
-        <v>2.263915880756588</v>
-      </c>
-      <c r="AI35" s="15">
+        <v>2.02130763274462</v>
+      </c>
+      <c r="AJ35" s="15">
         <f t="shared" si="15"/>
-        <v>2.02130763274462</v>
-      </c>
-      <c r="AJ35" s="15">
+        <v>2.6488877194626346</v>
+      </c>
+      <c r="AK35" s="15">
         <f t="shared" si="16"/>
-        <v>2.6488877194626346</v>
-      </c>
-      <c r="AK35" s="15">
+        <v>0.23692211719918735</v>
+      </c>
+      <c r="AL35" s="15">
         <f t="shared" si="17"/>
-        <v>0.23692211719918735</v>
-      </c>
-      <c r="AL35" s="15">
-        <f t="shared" si="18"/>
         <v>0.31048222277074106</v>
       </c>
       <c r="AM35" s="14" t="s">
@@ -5864,7 +5864,7 @@
         <v>10.313099999999999</v>
       </c>
       <c r="W36" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>7.6164999999999985</v>
       </c>
       <c r="X36" s="15">
@@ -5908,23 +5908,23 @@
         <v>0.3716607506138585</v>
       </c>
       <c r="AH36" s="15">
+        <f t="shared" si="19"/>
+        <v>1.8502843157681905</v>
+      </c>
+      <c r="AI36" s="15">
         <f t="shared" si="14"/>
-        <v>1.8502843157681905</v>
-      </c>
-      <c r="AI36" s="15">
+        <v>1.3489372754452105</v>
+      </c>
+      <c r="AJ36" s="15">
         <f t="shared" si="15"/>
-        <v>1.3489372754452105</v>
-      </c>
-      <c r="AJ36" s="15">
+        <v>2.6428851965355653</v>
+      </c>
+      <c r="AK36" s="15">
         <f t="shared" si="16"/>
-        <v>2.6428851965355653</v>
-      </c>
-      <c r="AK36" s="15">
+        <v>0.48959671906541025</v>
+      </c>
+      <c r="AL36" s="15">
         <f t="shared" si="17"/>
-        <v>0.48959671906541025</v>
-      </c>
-      <c r="AL36" s="15">
-        <f t="shared" si="18"/>
         <v>0.9592350546197882</v>
       </c>
       <c r="AM36" s="14" t="s">
